--- a/26-2 Sports Day/26-2 Sports Day 기획 일정.xlsx
+++ b/26-2 Sports Day/26-2 Sports Day 기획 일정.xlsx
@@ -1153,7 +1153,7 @@
       <c r="B16" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="17"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="25"/>
       <c r="E16" s="26" t="s">
         <v>20</v>
